--- a/data/trans_dic/P45C_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 16,57</t>
+          <t>8,57; 16,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,53; 23,73</t>
+          <t>13,25; 22,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,65; 24,56</t>
+          <t>14,89; 24,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 19,6</t>
+          <t>10,52; 19,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,51; 18,19</t>
+          <t>9,85; 18,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,69; 19,03</t>
+          <t>10,79; 19,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,73; 16,9</t>
+          <t>10,94; 16,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,98; 19,69</t>
+          <t>12,7; 19,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,18; 20,83</t>
+          <t>14,17; 20,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,49</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,52; 28,38</t>
+          <t>20,27; 28,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,16; 15,23</t>
+          <t>9,52; 15,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,22; 15,75</t>
+          <t>9,99; 15,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,54; 22,4</t>
+          <t>13,4; 22,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,52; 23,56</t>
+          <t>16,7; 23,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 13,05</t>
+          <t>7,27; 12,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,59; 18,14</t>
+          <t>11,82; 17,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,85; 18,92</t>
+          <t>12,66; 18,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,47; 24,77</t>
+          <t>19,36; 24,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,99; 13,02</t>
+          <t>9,12; 13,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,54; 15,9</t>
+          <t>11,78; 15,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,04; 19,61</t>
+          <t>14,05; 19,58</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,97; 16,2</t>
+          <t>9,35; 16,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,3; 35,68</t>
+          <t>25,6; 35,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,54</t>
+          <t>6,14; 12,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 9,56</t>
+          <t>4,18; 9,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,31; 15,29</t>
+          <t>8,49; 15,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,94; 21,19</t>
+          <t>12,52; 21,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,24; 16,19</t>
+          <t>9,14; 16,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 10,61</t>
+          <t>5,3; 11,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,48; 14,7</t>
+          <t>9,6; 14,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,29; 26,5</t>
+          <t>20,09; 27,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,52; 13,42</t>
+          <t>8,66; 13,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,19</t>
+          <t>5,05; 9,23</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,29; 27,9</t>
+          <t>18,72; 27,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 16,21</t>
+          <t>9,37; 16,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,19; 17,65</t>
+          <t>10,28; 18,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 23,47</t>
+          <t>10,03; 23,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 16,36</t>
+          <t>9,6; 16,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 11,61</t>
+          <t>5,31; 11,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 14,87</t>
+          <t>8,34; 14,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 12,19</t>
+          <t>5,32; 12,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,97; 20,58</t>
+          <t>14,98; 20,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 12,63</t>
+          <t>8,23; 13,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,07; 15,04</t>
+          <t>10,05; 15,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 15,12</t>
+          <t>8,01; 15,25</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,97</t>
+          <t>3,11; 9,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 15,92</t>
+          <t>7,11; 16,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,73</t>
+          <t>1,36; 7,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,47</t>
+          <t>3,16; 9,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 9,98</t>
+          <t>3,64; 9,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,68; 15,62</t>
+          <t>7,25; 15,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,2</t>
+          <t>2,25; 7,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 8,62</t>
+          <t>4,02; 8,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,31; 14,1</t>
+          <t>8,0; 14,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,77</t>
+          <t>0,84; 3,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,13</t>
+          <t>3,26; 7,1</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,82; 31,8</t>
+          <t>20,14; 31,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,67; 38,92</t>
+          <t>26,92; 38,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,63</t>
+          <t>0,79; 4,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,75; 28,11</t>
+          <t>17,7; 27,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,58; 21,13</t>
+          <t>12,62; 20,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,69; 28,72</t>
+          <t>18,09; 28,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,04</t>
+          <t>2,19; 6,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,21; 34,02</t>
+          <t>25,04; 34,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,61; 24,33</t>
+          <t>17,61; 25,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,49; 32,31</t>
+          <t>24,53; 32,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,01</t>
+          <t>2,0; 5,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,8; 29,42</t>
+          <t>22,4; 29,32</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,56; 16,15</t>
+          <t>10,47; 16,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,15; 28,85</t>
+          <t>22,54; 29,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,38; 17,31</t>
+          <t>11,75; 17,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,13; 17,01</t>
+          <t>10,36; 17,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,64; 12,31</t>
+          <t>7,67; 12,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,18; 24,64</t>
+          <t>18,67; 25,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,45; 19,23</t>
+          <t>13,59; 19,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,68; 14,11</t>
+          <t>4,86; 14,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,61; 13,22</t>
+          <t>9,53; 13,31</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,17; 26,05</t>
+          <t>21,29; 26,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,23; 17,5</t>
+          <t>13,19; 17,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,01; 14,32</t>
+          <t>7,27; 14,24</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,4; 13,25</t>
+          <t>8,67; 13,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,57</t>
+          <t>5,85; 9,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,42; 22,06</t>
+          <t>16,32; 22,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,58; 33,51</t>
+          <t>11,67; 33,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,26; 11,68</t>
+          <t>7,46; 11,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,62; 9,34</t>
+          <t>5,74; 9,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,74; 21,22</t>
+          <t>16,04; 21,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,53; 20,72</t>
+          <t>15,84; 20,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,56; 11,55</t>
+          <t>8,65; 11,69</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,85</t>
+          <t>6,09; 8,75</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16,93; 20,83</t>
+          <t>16,92; 20,84</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,85; 25,87</t>
+          <t>13,26; 25,86</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14,4; 16,93</t>
+          <t>14,42; 17,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,3; 18,91</t>
+          <t>16,22; 18,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,39; 14,88</t>
+          <t>12,22; 14,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,39; 17,27</t>
+          <t>12,05; 17,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,29; 13,53</t>
+          <t>11,4; 13,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,23; 14,66</t>
+          <t>12,26; 14,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,43; 14,69</t>
+          <t>12,39; 14,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,16; 13,69</t>
+          <t>10,05; 13,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,16; 14,92</t>
+          <t>13,15; 14,93</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14,67; 16,4</t>
+          <t>14,62; 16,41</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12,65; 14,43</t>
+          <t>12,73; 14,33</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,04; 15,0</t>
+          <t>11,95; 15,06</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24439; 45241</t>
+          <t>23403; 46330</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42835; 69928</t>
+          <t>39040; 67713</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43045; 72155</t>
+          <t>43754; 73171</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1801</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27624; 51135</t>
+          <t>27451; 51642</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27020; 51653</t>
+          <t>27970; 52888</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30765; 54772</t>
+          <t>31065; 55682</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2134</t>
+          <t>0; 2587</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57261; 90201</t>
+          <t>58401; 88078</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75103; 113980</t>
+          <t>73492; 112425</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82457; 121120</t>
+          <t>82418; 121272</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2595</t>
+          <t>0; 2933</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>101173; 139940</t>
+          <t>99923; 138431</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45656; 75919</t>
+          <t>47436; 75964</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50944; 78498</t>
+          <t>49806; 79394</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69979; 115797</t>
+          <t>69275; 115672</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83261; 118718</t>
+          <t>84156; 120225</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38695; 66974</t>
+          <t>37321; 65174</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60346; 94464</t>
+          <t>61570; 93463</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66111; 97299</t>
+          <t>65124; 96744</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>194129; 246950</t>
+          <t>192982; 246278</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90965; 131712</t>
+          <t>92288; 134524</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>117606; 162077</t>
+          <t>120048; 162966</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>144811; 202299</t>
+          <t>144861; 201942</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28588; 51663</t>
+          <t>29819; 52752</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81735; 115301</t>
+          <t>82729; 114529</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19975; 39553</t>
+          <t>19357; 40269</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12797; 30166</t>
+          <t>13191; 30001</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27872; 51277</t>
+          <t>28488; 50843</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43834; 71771</t>
+          <t>42422; 71171</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30789; 53916</t>
+          <t>30449; 53954</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17355; 37046</t>
+          <t>18497; 39099</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62054; 96161</t>
+          <t>62804; 94123</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>134303; 175365</t>
+          <t>132944; 179374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55242; 87047</t>
+          <t>56178; 86710</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34497; 61106</t>
+          <t>33547; 61345</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69191; 100069</t>
+          <t>67130; 99075</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33059; 59756</t>
+          <t>34546; 60498</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37619; 65131</t>
+          <t>37937; 66979</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31105; 72804</t>
+          <t>31105; 73675</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35176; 60774</t>
+          <t>35674; 60679</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22205; 44542</t>
+          <t>20363; 44275</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33070; 57298</t>
+          <t>32130; 57626</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25733; 57984</t>
+          <t>25304; 57193</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>109313; 150271</t>
+          <t>109359; 149934</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60636; 95057</t>
+          <t>61923; 98071</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75934; 113467</t>
+          <t>75828; 115869</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63302; 118848</t>
+          <t>62991; 119893</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6012; 20277</t>
+          <t>6327; 19339</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15299; 33840</t>
+          <t>15126; 34012</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3315; 14220</t>
+          <t>2874; 14791</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5579; 16922</t>
+          <t>5644; 16625</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7462; 20735</t>
+          <t>7568; 20390</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16781; 34148</t>
+          <t>15840; 34117</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4161</t>
+          <t>0; 4439</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4517; 15005</t>
+          <t>4681; 16602</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17521; 35427</t>
+          <t>16502; 34733</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35817; 60785</t>
+          <t>34509; 61976</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3684; 16188</t>
+          <t>3595; 15329</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11935; 27611</t>
+          <t>12615; 27480</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>56375; 86120</t>
+          <t>54552; 83963</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>75275; 105903</t>
+          <t>73251; 105784</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2023; 12126</t>
+          <t>2064; 11998</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47711; 75560</t>
+          <t>47595; 74053</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34991; 58762</t>
+          <t>35098; 58084</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52329; 80432</t>
+          <t>50662; 78948</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5865; 19148</t>
+          <t>5948; 19032</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>62225; 87452</t>
+          <t>64361; 87478</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>96693; 133568</t>
+          <t>96646; 137397</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>135201; 178364</t>
+          <t>135454; 179637</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10029; 26774</t>
+          <t>10679; 26851</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>119911; 154725</t>
+          <t>117795; 154204</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>64967; 99331</t>
+          <t>64423; 99246</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>146137; 190360</t>
+          <t>148694; 193164</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>73307; 111475</t>
+          <t>75683; 113355</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63022; 105825</t>
+          <t>64436; 107257</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>48697; 78446</t>
+          <t>48879; 78845</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>125558; 170181</t>
+          <t>128953; 174170</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>91113; 130296</t>
+          <t>92091; 130246</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>39724; 119795</t>
+          <t>41248; 122663</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>120310; 165569</t>
+          <t>119284; 166738</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>285913; 351750</t>
+          <t>287466; 351626</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>174795; 231293</t>
+          <t>174313; 230668</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>103074; 210754</t>
+          <t>106895; 209573</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>61868; 97508</t>
+          <t>63820; 96083</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>45191; 73670</t>
+          <t>44979; 73405</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>126636; 170133</t>
+          <t>125906; 170315</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>98273; 311227</t>
+          <t>108380; 312986</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>56386; 90668</t>
+          <t>57881; 90202</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>45758; 76055</t>
+          <t>46777; 74982</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>129518; 174595</t>
+          <t>131999; 176449</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>111204; 148353</t>
+          <t>113413; 149480</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>129531; 174662</t>
+          <t>130778; 176779</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>99365; 140177</t>
+          <t>96387; 138597</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>269897; 331985</t>
+          <t>269709; 332293</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>211272; 425419</t>
+          <t>218017; 425338</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>470835; 553488</t>
+          <t>471293; 558570</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>553901; 642646</t>
+          <t>551193; 641753</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>417035; 500918</t>
+          <t>411298; 496714</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>427918; 596289</t>
+          <t>415959; 602016</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>380482; 456084</t>
+          <t>384174; 457603</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>430882; 516401</t>
+          <t>431953; 515392</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>437175; 516935</t>
+          <t>436026; 517030</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>371769; 501114</t>
+          <t>367559; 499047</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>873613; 990516</t>
+          <t>873195; 991115</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1015275; 1135391</t>
+          <t>1012265; 1136203</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>870594; 993009</t>
+          <t>876401; 986589</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>856184; 1066815</t>
+          <t>850031; 1071214</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P45C_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R2-Provincia-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,57; 16,97</t>
+          <t>9,0; 16,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,25; 22,97</t>
+          <t>14,01; 23,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,89; 24,91</t>
+          <t>15,17; 25,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,52; 19,8</t>
+          <t>10,56; 19,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,85; 18,62</t>
+          <t>9,45; 18,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,79; 19,35</t>
+          <t>10,95; 18,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,94; 16,5</t>
+          <t>10,9; 16,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,7; 19,43</t>
+          <t>12,89; 19,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,17; 20,85</t>
+          <t>13,75; 20,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,49</t>
+          <t>0,0; 0,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,27; 28,07</t>
+          <t>20,35; 27,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 15,24</t>
+          <t>9,43; 15,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 15,93</t>
+          <t>10,1; 16,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,4; 22,37</t>
+          <t>13,58; 21,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,7; 23,86</t>
+          <t>16,82; 24,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 12,7</t>
+          <t>7,34; 12,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 17,94</t>
+          <t>11,94; 18,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,66; 18,81</t>
+          <t>12,75; 18,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,36; 24,7</t>
+          <t>19,47; 24,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 13,3</t>
+          <t>9,23; 13,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,78; 15,99</t>
+          <t>11,55; 16,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,05; 19,58</t>
+          <t>13,93; 18,99</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,35; 16,54</t>
+          <t>9,21; 16,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,6; 35,45</t>
+          <t>25,31; 35,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 12,77</t>
+          <t>6,37; 12,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,51</t>
+          <t>4,3; 10,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,49; 15,16</t>
+          <t>8,67; 15,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,52; 21,01</t>
+          <t>13,01; 21,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,14; 16,2</t>
+          <t>9,15; 16,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 11,2</t>
+          <t>5,15; 10,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,6; 14,39</t>
+          <t>9,68; 14,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,09; 27,1</t>
+          <t>19,83; 26,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,66; 13,37</t>
+          <t>8,72; 13,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 9,23</t>
+          <t>5,55; 9,46</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,72; 27,62</t>
+          <t>18,71; 27,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 16,41</t>
+          <t>9,05; 16,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 18,15</t>
+          <t>10,59; 17,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 23,75</t>
+          <t>9,99; 20,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 16,34</t>
+          <t>9,48; 16,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 11,54</t>
+          <t>5,47; 11,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,34; 14,95</t>
+          <t>8,23; 15,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,02</t>
+          <t>8,48; 14,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,98; 20,54</t>
+          <t>14,86; 20,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,23; 13,03</t>
+          <t>7,99; 12,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 15,36</t>
+          <t>10,42; 15,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,01; 15,25</t>
+          <t>10,17; 16,51</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 9,51</t>
+          <t>2,98; 9,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,11; 16,0</t>
+          <t>7,16; 15,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,0</t>
+          <t>1,36; 6,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 9,3</t>
+          <t>3,63; 9,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 9,82</t>
+          <t>3,82; 10,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 15,61</t>
+          <t>6,98; 15,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,97</t>
+          <t>2,07; 7,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,45</t>
+          <t>4,03; 8,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,0; 14,37</t>
+          <t>8,3; 14,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,57</t>
+          <t>0,84; 3,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,1</t>
+          <t>3,18; 7,16</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,14; 31,0</t>
+          <t>20,1; 31,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,92; 38,88</t>
+          <t>27,86; 39,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,58</t>
+          <t>0,78; 4,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,7; 27,55</t>
+          <t>17,23; 26,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,62; 20,88</t>
+          <t>12,4; 21,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,09; 28,19</t>
+          <t>18,43; 29,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,99</t>
+          <t>2,16; 6,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,04; 34,03</t>
+          <t>25,12; 34,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,61; 25,03</t>
+          <t>17,54; 24,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,53; 32,54</t>
+          <t>24,61; 31,98</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,03</t>
+          <t>2,0; 5,15</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,4; 29,32</t>
+          <t>22,48; 28,51</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,47; 16,14</t>
+          <t>10,27; 15,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,54; 29,27</t>
+          <t>22,29; 29,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,75; 17,6</t>
+          <t>11,73; 17,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,36; 17,24</t>
+          <t>11,45; 18,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,67; 12,37</t>
+          <t>7,6; 12,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,67; 25,22</t>
+          <t>18,55; 24,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,59; 19,22</t>
+          <t>13,36; 19,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,86; 14,45</t>
+          <t>11,14; 16,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,53; 13,31</t>
+          <t>9,8; 13,43</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,29; 26,04</t>
+          <t>21,36; 25,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,19; 17,45</t>
+          <t>13,33; 17,42</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 14,24</t>
+          <t>12,16; 16,27</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,67; 13,05</t>
+          <t>8,48; 12,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,85; 9,54</t>
+          <t>5,62; 9,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,32; 22,08</t>
+          <t>16,45; 22,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,67; 33,7</t>
+          <t>29,06; 36,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,46; 11,62</t>
+          <t>7,41; 12,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,21</t>
+          <t>5,54; 9,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,04; 21,44</t>
+          <t>16,03; 21,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,84; 20,88</t>
+          <t>15,61; 20,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,65; 11,69</t>
+          <t>8,5; 11,57</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,09; 8,75</t>
+          <t>6,27; 8,91</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16,92; 20,84</t>
+          <t>16,66; 20,68</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,26; 25,86</t>
+          <t>22,71; 27,1</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14,42; 17,09</t>
+          <t>14,45; 17,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,22; 18,88</t>
+          <t>16,22; 18,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,22; 14,76</t>
+          <t>12,24; 14,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,05; 17,44</t>
+          <t>15,51; 18,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,4; 13,57</t>
+          <t>11,29; 13,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,26; 14,63</t>
+          <t>12,43; 14,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,39; 14,7</t>
+          <t>12,43; 14,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,05; 13,64</t>
+          <t>12,32; 14,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,15; 14,93</t>
+          <t>13,26; 14,89</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14,62; 16,41</t>
+          <t>14,62; 16,35</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12,73; 14,33</t>
+          <t>12,73; 14,4</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,95; 15,06</t>
+          <t>14,26; 16,07</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>493</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>493</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23403; 46330</t>
+          <t>24584; 45909</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39040; 67713</t>
+          <t>41297; 70297</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43754; 73171</t>
+          <t>44569; 73631</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2229,42 +2229,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27451; 51642</t>
+          <t>27551; 50704</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27970; 52888</t>
+          <t>26830; 51456</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31065; 55682</t>
+          <t>31506; 54214</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2587</t>
+          <t>0; 2526</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58401; 88078</t>
+          <t>58177; 90334</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>73492; 112425</t>
+          <t>74595; 110797</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82418; 121272</t>
+          <t>79946; 117082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2933</t>
+          <t>0; 2453</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90694</t>
+          <t>90766</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>81281</t>
+          <t>84810</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>171974</t>
+          <t>175576</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>99923; 138431</t>
+          <t>100325; 137691</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47436; 75964</t>
+          <t>47007; 76812</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49806; 79394</t>
+          <t>50325; 80869</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69275; 115672</t>
+          <t>71862; 114623</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84156; 120225</t>
+          <t>84754; 121098</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37321; 65174</t>
+          <t>37684; 64942</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61570; 93463</t>
+          <t>62179; 94922</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65124; 96744</t>
+          <t>69616; 102020</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>192982; 246278</t>
+          <t>194120; 248582</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92288; 134524</t>
+          <t>93404; 133655</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120048; 162966</t>
+          <t>117697; 164478</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>144861; 201942</t>
+          <t>149779; 204214</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>21605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26793</t>
+          <t>26694</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46552</t>
+          <t>48299</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29819; 52752</t>
+          <t>29377; 52360</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>82729; 114529</t>
+          <t>81788; 114998</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19357; 40269</t>
+          <t>20104; 40145</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13191; 30001</t>
+          <t>13572; 32294</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28488; 50843</t>
+          <t>29066; 51428</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42422; 71171</t>
+          <t>44067; 72625</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30449; 53954</t>
+          <t>30489; 53469</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18497; 39099</t>
+          <t>18339; 38379</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62804; 94123</t>
+          <t>63362; 96420</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>132944; 179374</t>
+          <t>131215; 177890</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56178; 86710</t>
+          <t>56532; 87397</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33547; 61345</t>
+          <t>37306; 63518</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45651</t>
+          <t>54788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>47018</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88222</t>
+          <t>101806</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67130; 99075</t>
+          <t>67117; 98318</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34546; 60498</t>
+          <t>33367; 60003</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37937; 66979</t>
+          <t>39082; 66162</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31105; 73675</t>
+          <t>37035; 76797</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35674; 60679</t>
+          <t>35231; 59897</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20363; 44275</t>
+          <t>21002; 44601</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32130; 57626</t>
+          <t>31733; 57975</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25304; 57193</t>
+          <t>35784; 60424</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>109359; 149934</t>
+          <t>108529; 149590</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>61923; 98071</t>
+          <t>60091; 96522</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75828; 115869</t>
+          <t>78633; 116568</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>62991; 119893</t>
+          <t>80649; 130835</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18452</t>
+          <t>20728</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6327; 19339</t>
+          <t>6065; 19912</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15126; 34012</t>
+          <t>15225; 33281</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2874; 14791</t>
+          <t>2874; 14205</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5644; 16625</t>
+          <t>7462; 20333</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7568; 20390</t>
+          <t>7924; 21979</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15840; 34117</t>
+          <t>15262; 33726</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4439</t>
+          <t>0; 4200</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4681; 16602</t>
+          <t>4699; 16189</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16502; 34733</t>
+          <t>16548; 34931</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34509; 61976</t>
+          <t>35778; 61976</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3595; 15329</t>
+          <t>3628; 15936</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12615; 27480</t>
+          <t>13739; 30984</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60279</t>
+          <t>57789</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>75354</t>
+          <t>77082</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>135633</t>
+          <t>134872</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>54552; 83963</t>
+          <t>54438; 84183</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73251; 105784</t>
+          <t>75794; 106640</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2064; 11998</t>
+          <t>2043; 12137</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47595; 74053</t>
+          <t>46501; 71421</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35098; 58084</t>
+          <t>34496; 59212</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50662; 78948</t>
+          <t>51596; 81295</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5948; 19032</t>
+          <t>5886; 18289</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>64361; 87478</t>
+          <t>66251; 91298</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>96646; 137397</t>
+          <t>96307; 134404</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>135454; 179637</t>
+          <t>135872; 176541</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10679; 26851</t>
+          <t>10702; 27522</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>117795; 154204</t>
+          <t>119942; 152165</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>84330</t>
+          <t>103965</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>85055</t>
+          <t>104492</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>169384</t>
+          <t>208457</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>64423; 99246</t>
+          <t>63182; 96228</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>148694; 193164</t>
+          <t>147089; 193629</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75683; 113355</t>
+          <t>75584; 114748</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>64436; 107257</t>
+          <t>82113; 129975</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>48879; 78845</t>
+          <t>48444; 78392</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>128953; 174170</t>
+          <t>128140; 172543</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92091; 130246</t>
+          <t>90506; 129397</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>41248; 122663</t>
+          <t>85871; 128506</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>119284; 166738</t>
+          <t>122780; 168166</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>287466; 351626</t>
+          <t>288498; 350415</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>174313; 230668</t>
+          <t>176207; 230195</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>106895; 209573</t>
+          <t>180967; 242163</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>221466</t>
+          <t>256996</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>130263</t>
+          <t>148362</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>351729</t>
+          <t>405358</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>63820; 96083</t>
+          <t>62436; 95481</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>44979; 73405</t>
+          <t>43285; 75085</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>125906; 170315</t>
+          <t>126844; 171727</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>108380; 312986</t>
+          <t>231948; 287968</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>57881; 90202</t>
+          <t>57486; 93237</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>46777; 74982</t>
+          <t>45136; 74125</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>131999; 176449</t>
+          <t>131863; 176733</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>113413; 149480</t>
+          <t>129455; 169831</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>130778; 176779</t>
+          <t>128585; 174951</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>96387; 138597</t>
+          <t>99265; 141086</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>269709; 332293</t>
+          <t>265534; 329638</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>218017; 425338</t>
+          <t>369567; 440911</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>532017</t>
+          <t>598199</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>450443</t>
+          <t>497389</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>982460</t>
+          <t>1095588</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>471293; 558570</t>
+          <t>472239; 557285</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>551193; 641753</t>
+          <t>551494; 643560</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>411298; 496714</t>
+          <t>411999; 493086</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>415959; 602016</t>
+          <t>546737; 656550</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>384174; 457603</t>
+          <t>380718; 459893</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>431953; 515392</t>
+          <t>438102; 517413</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>436026; 517030</t>
+          <t>437319; 520957</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>367559; 499047</t>
+          <t>459725; 538703</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>873195; 991115</t>
+          <t>880119; 988972</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1012265; 1136203</t>
+          <t>1012196; 1131831</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>876401; 986589</t>
+          <t>876199; 990913</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>850031; 1071214</t>
+          <t>1034481; 1166270</t>
         </is>
       </c>
     </row>
